--- a/Docs/trainloop-monetizace.xlsx
+++ b/Docs/trainloop-monetizace.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marek\Desktop\school\Magistr\3-sem\agile-dev\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jumbo\team-7\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AC3060-3C88-408A-B230-A04456A2CCB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBAD1BE8-F1D8-4F3E-9CCF-65793CA20D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Přehled" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Reklamy" sheetId="3" r:id="rId3"/>
     <sheet name="Výpočty a citlivost" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -776,12 +776,6 @@
   </cellStyleXfs>
   <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -812,9 +806,15 @@
     <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normální" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1087,151 +1087,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
     </row>
     <row r="6" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
     </row>
     <row r="8" spans="1:5" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
     </row>
     <row r="10" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="6">
         <f>'Výpočty a citlivost'!B25</f>
         <v>3740</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="6">
         <f>'Výpočty a citlivost'!C25</f>
         <v>13570</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="6">
         <f>'Výpočty a citlivost'!D25</f>
         <v>28210</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="6">
         <f>'Výpočty a citlivost'!E25</f>
         <v>141080</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="6">
         <f>'Výpočty a citlivost'!B26</f>
         <v>340</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="6">
         <f>'Výpočty a citlivost'!C26</f>
         <v>1550</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="6">
         <f>'Výpočty a citlivost'!D26</f>
         <v>4260</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="6">
         <f>'Výpočty a citlivost'!E26</f>
         <v>29240</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="8">
         <f>'Výpočty a citlivost'!B27</f>
         <v>4080</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="8">
         <f>'Výpočty a citlivost'!C27</f>
         <v>15120</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="8">
         <f>'Výpočty a citlivost'!D27</f>
         <v>32470</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="8">
         <f>'Výpočty a citlivost'!E27</f>
         <v>170320</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="8">
         <f>'Výpočty a citlivost'!B28</f>
         <v>48960</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="8">
         <f>'Výpočty a citlivost'!C28</f>
         <v>181440</v>
       </c>
-      <c r="D14" s="10">
-        <f>'Výpočty a citlivost'!D28</f>
+      <c r="D14" s="8">
+        <f>'Výpočty a citlivost'!D29</f>
         <v>389640</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="8">
         <f>'Výpočty a citlivost'!E28</f>
         <v>2043840</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1261,487 +1261,487 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
     </row>
     <row r="6" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="10">
         <v>0</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="11">
         <v>0</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="12">
         <v>0</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="10">
         <v>0</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="10">
         <v>99</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="11">
         <v>3.99</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="12">
         <v>4.99</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="10">
         <v>790</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="5" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="10">
         <v>29</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="11">
         <v>0.99</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="12">
         <v>0.99</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="10">
         <v>199</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="11">
         <v>7.99</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="12">
         <v>8.99</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="10">
         <v>1990</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="5" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="10">
         <v>399</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="11">
         <v>15.99</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="12">
         <v>17.989999999999998</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="10">
         <v>3990</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="5" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="10">
         <v>549</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="11">
         <v>21.99</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="12">
         <v>24.99</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="5" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="10">
         <v>1090</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="11">
         <v>43.99</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="12">
         <v>49.99</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="5" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="10">
         <v>1990</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="11">
         <v>79.989999999999995</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="12">
         <v>89.99</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6" t="s">
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="12">
         <v>11.99</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="13">
         <f t="shared" ref="D18:D26" si="0">C18*21</f>
         <v>251.79</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="5" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="12">
         <v>12.99</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="13">
         <f t="shared" si="0"/>
         <v>272.79000000000002</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="12">
         <v>13.99</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="13">
         <f t="shared" si="0"/>
         <v>293.79000000000002</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="12">
         <v>9.99</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="13">
         <f t="shared" si="0"/>
         <v>209.79</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" s="5" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="12">
         <v>40</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="13">
         <f t="shared" si="0"/>
         <v>840</v>
       </c>
-      <c r="G22" s="7" t="s">
+      <c r="G22" s="5" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="12">
         <v>29</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="13">
         <f t="shared" si="0"/>
         <v>609</v>
       </c>
-      <c r="G23" s="7" t="s">
+      <c r="G23" s="5" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="12">
         <v>44.99</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="13">
         <f t="shared" si="0"/>
         <v>944.79000000000008</v>
       </c>
-      <c r="G24" s="7" t="s">
+      <c r="G24" s="5" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="12">
         <v>49</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="13">
         <f t="shared" si="0"/>
         <v>1029</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="G25" s="5" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="14">
+      <c r="C26" s="12">
         <v>95</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="13">
         <f t="shared" si="0"/>
         <v>1995</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="G26" s="5" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6" t="s">
+      <c r="B28" s="4"/>
+      <c r="C28" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6" t="s">
+      <c r="F28" s="4"/>
+      <c r="G28" s="4" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="13">
         <f>MEDIAN(D18:D22)</f>
         <v>272.79000000000002</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="6">
         <f>C8</f>
         <v>99</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="14">
         <f>1-D29/C29</f>
         <v>0.63708347080171568</v>
       </c>
-      <c r="G29" s="7" t="s">
+      <c r="G29" s="5" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="15">
+      <c r="C30" s="13">
         <f>MEDIAN(D23:D26)</f>
         <v>986.89499999999998</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="6">
         <f>C10</f>
         <v>199</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="14">
         <f>1-D30/C30</f>
         <v>0.79835747470602247</v>
       </c>
-      <c r="G30" s="7" t="s">
+      <c r="G30" s="5" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="13">
         <f>C30</f>
         <v>986.89499999999998</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="6">
         <f>C11</f>
         <v>399</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="14">
         <f>1-D31/C31</f>
         <v>0.59570167039046706</v>
       </c>
-      <c r="G31" s="7" t="s">
+      <c r="G31" s="5" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1770,240 +1770,240 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="6" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F6" s="6"/>
+      <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="15">
         <v>34</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="10">
         <v>3</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="10">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="15">
         <v>6</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="10">
         <v>20</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="10">
         <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="15">
         <v>1</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="10">
         <v>45</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="10">
         <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="19">
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17">
         <f>SUMPRODUCT($C$7:$C$9,D7:D9)/1000</f>
         <v>0.26700000000000002</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="17">
         <f>SUMPRODUCT($C$7:$C$9,E7:E9)/1000</f>
         <v>0.93</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6" t="s">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="18">
         <f>'Výpočty a citlivost'!B6</f>
         <v>1500</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="18">
         <f>'Výpočty a citlivost'!C6</f>
         <v>5000</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="18">
         <f>'Výpočty a citlivost'!D6</f>
         <v>10000</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="18">
         <f>'Výpočty a citlivost'!E6</f>
         <v>50000</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="19">
         <v>0.02</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="19">
         <v>0.18</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="19">
         <v>0.4</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="19">
         <v>0.7</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="19">
         <v>0.8</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="19">
         <v>0.8</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="19">
         <v>0.8</v>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="19">
         <v>0.8</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="20">
         <f>(1-C14)*$D$10+C14*$E$10</f>
         <v>0.28026000000000001</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="20">
         <f>(1-D14)*$D$10+D14*$E$10</f>
         <v>0.38634000000000002</v>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="20">
         <f>(1-E14)*$D$10+E14*$E$10</f>
         <v>0.53220000000000001</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="20">
         <f>(1-F14)*$D$10+F14*$E$10</f>
         <v>0.73110000000000008</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B17" s="18"/>
-      <c r="C17" s="23">
+      <c r="B17" s="16"/>
+      <c r="C17" s="21">
         <f>ROUND(C13*C15*C16,-1)</f>
         <v>340</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="21">
         <f>ROUND(D13*D15*D16,-1)</f>
         <v>1550</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="21">
         <f>ROUND(E13*E15*E16,-1)</f>
         <v>4260</v>
       </c>
-      <c r="F17" s="23">
+      <c r="F17" s="21">
         <f>ROUND(F13*F15*F16,-1)</f>
         <v>29240</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2029,527 +2029,529 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="6"/>
+      <c r="F5" s="4"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="15">
         <v>1500</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="15">
         <v>5000</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="15">
         <v>10000</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="15">
         <v>50000</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6" t="s">
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="22">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="19">
         <v>0.85</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="5" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="23">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="24">
         <v>3</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="5" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="19">
         <v>0.7</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="5" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="19">
         <v>0.6</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="5" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6" t="s">
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B17" s="27">
+      <c r="B17" s="25">
         <f>($B$14*'Ceník a konkurence'!F8/12+(1-$B$14)*'Ceník a konkurence'!C8)*$B$13</f>
         <v>55.36999999999999</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="5" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B18" s="27">
+      <c r="B18" s="25">
         <f>(0.65*($B$14*'Ceník a konkurence'!F10/12+(1-$B$14)*'Ceník a konkurence'!C10)+0.35*($B$14*'Ceník a konkurence'!F11/12+(1-$B$14)*'Ceník a konkurence'!C11))*$B$13</f>
         <v>169.47</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="5" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="6">
         <f>'Ceník a konkurence'!C13</f>
         <v>1090</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="5" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="4" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="13">
         <f>ROUND(B6*$B$10*$B$9*$B$17,-1)</f>
         <v>2470</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="13">
         <f>ROUND(C6*$B$10*$B$9*$B$17,-1)</f>
         <v>8240</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="13">
         <f>ROUND(D6*$B$10*$B$9*$B$17,-1)</f>
         <v>16470</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="13">
         <f>ROUND(E6*$B$10*$B$9*$B$17,-1)</f>
         <v>82360</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="5" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="13">
         <f>ROUND(B6*$B$11*$B$18,-1)</f>
         <v>1270</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="13">
         <f>ROUND(C6*$B$11*$B$18,-1)</f>
         <v>4240</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="13">
         <f>ROUND(D6*$B$11*$B$18,-1)</f>
         <v>8470</v>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="13">
         <f>ROUND(E6*$B$11*$B$18,-1)</f>
         <v>42370</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="5" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="13">
         <f>ROUNDDOWN(B6/10000*$B$12,0)*$B$19</f>
         <v>0</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="13">
         <f>ROUNDDOWN(C6/10000*$B$12,0)*$B$19</f>
         <v>1090</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="13">
         <f>ROUNDDOWN(D6/10000*$B$12,0)*$B$19</f>
         <v>3270</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="13">
         <f>ROUNDDOWN(E6/10000*$B$12,0)*$B$19</f>
         <v>16350</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="5" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="B25" s="27">
+      <c r="B25" s="25">
         <f>SUM(B22:B24)</f>
         <v>3740</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="25">
         <f>SUM(C22:C24)</f>
         <v>13570</v>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="25">
         <f>SUM(D22:D24)</f>
         <v>28210</v>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="25">
         <f>SUM(E22:E24)</f>
         <v>141080</v>
       </c>
-      <c r="F25" s="7"/>
+      <c r="F25" s="5"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="6">
         <f>Reklamy!C17</f>
         <v>340</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="6">
         <f>Reklamy!D17</f>
         <v>1550</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="6">
         <f>Reklamy!E17</f>
         <v>4260</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="6">
         <f>Reklamy!F17</f>
         <v>29240</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="5" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B27" s="21">
         <f>B25+B26</f>
         <v>4080</v>
       </c>
-      <c r="C27" s="23">
+      <c r="C27" s="21">
         <f>C25+C26</f>
         <v>15120</v>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="21">
         <f>D25+D26</f>
         <v>32470</v>
       </c>
-      <c r="E27" s="23">
+      <c r="E27" s="21">
         <f>E25+E26</f>
         <v>170320</v>
       </c>
-      <c r="F27" s="28"/>
+      <c r="F27" s="26"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B28" s="21">
         <f>B27*12</f>
         <v>48960</v>
       </c>
-      <c r="C28" s="23">
+      <c r="C28" s="21">
         <f>C27*12</f>
         <v>181440</v>
       </c>
-      <c r="D28" s="23">
+      <c r="E28" s="21">
+        <f>E27*12</f>
+        <v>2043840</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D29" s="21">
         <f>D27*12</f>
         <v>389640</v>
       </c>
-      <c r="E28" s="23">
-        <f>E27*12</f>
-        <v>2043840</v>
-      </c>
-      <c r="F28" s="28" t="s">
-        <v>129</v>
-      </c>
     </row>
     <row r="30" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="4" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B31" s="15">
+      <c r="B31" s="13">
         <f>ROUND(B$6*$B$10*0.02*$B$17,-1)+B$23+B$24</f>
         <v>2680</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="13">
         <f>ROUND(C$6*$B$10*0.02*$B$17,-1)+C$23+C$24</f>
         <v>10040</v>
       </c>
-      <c r="D31" s="15">
+      <c r="D31" s="13">
         <f>ROUND(D$6*$B$10*0.02*$B$17,-1)+D$23+D$24</f>
         <v>21150</v>
       </c>
-      <c r="E31" s="15">
+      <c r="E31" s="13">
         <f>ROUND(E$6*$B$10*0.02*$B$17,-1)+E$23+E$24</f>
         <v>105780</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="28" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B32" s="15">
+      <c r="B32" s="13">
         <f>ROUND(B$6*$B$10*0.025*$B$17,-1)+B$23+B$24</f>
         <v>3030</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="13">
         <f>ROUND(C$6*$B$10*0.025*$B$17,-1)+C$23+C$24</f>
         <v>11210</v>
       </c>
-      <c r="D32" s="15">
+      <c r="D32" s="13">
         <f>ROUND(D$6*$B$10*0.025*$B$17,-1)+D$23+D$24</f>
         <v>23510</v>
       </c>
-      <c r="E32" s="15">
+      <c r="E32" s="13">
         <f>ROUND(E$6*$B$10*0.025*$B$17,-1)+E$23+E$24</f>
         <v>117550</v>
       </c>
-      <c r="F32" s="1"/>
+      <c r="F32" s="28"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B33" s="15">
+      <c r="B33" s="13">
         <f>ROUND(B$6*$B$10*0.03*$B$17,-1)+B$23+B$24</f>
         <v>3390</v>
       </c>
-      <c r="C33" s="15">
+      <c r="C33" s="13">
         <f>ROUND(C$6*$B$10*0.03*$B$17,-1)+C$23+C$24</f>
         <v>12390</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="13">
         <f>ROUND(D$6*$B$10*0.03*$B$17,-1)+D$23+D$24</f>
         <v>25860</v>
       </c>
-      <c r="E33" s="15">
+      <c r="E33" s="13">
         <f>ROUND(E$6*$B$10*0.03*$B$17,-1)+E$23+E$24</f>
         <v>129320</v>
       </c>
-      <c r="F33" s="1"/>
+      <c r="F33" s="28"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B34" s="21">
         <f>ROUND(B$6*$B$10*0.035*$B$17,-1)+B$23+B$24</f>
         <v>3740</v>
       </c>
-      <c r="C34" s="23">
+      <c r="C34" s="21">
         <f>ROUND(C$6*$B$10*0.035*$B$17,-1)+C$23+C$24</f>
         <v>13570</v>
       </c>
-      <c r="D34" s="23">
+      <c r="D34" s="21">
         <f>ROUND(D$6*$B$10*0.035*$B$17,-1)+D$23+D$24</f>
         <v>28210</v>
       </c>
-      <c r="E34" s="23">
+      <c r="E34" s="21">
         <f>ROUND(E$6*$B$10*0.035*$B$17,-1)+E$23+E$24</f>
         <v>141080</v>
       </c>
-      <c r="F34" s="1"/>
+      <c r="F34" s="28"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B35" s="15">
+      <c r="B35" s="13">
         <f>ROUND(B$6*$B$10*0.04*$B$17,-1)+B$23+B$24</f>
         <v>4090</v>
       </c>
-      <c r="C35" s="15">
+      <c r="C35" s="13">
         <f>ROUND(C$6*$B$10*0.04*$B$17,-1)+C$23+C$24</f>
         <v>14740</v>
       </c>
-      <c r="D35" s="15">
+      <c r="D35" s="13">
         <f>ROUND(D$6*$B$10*0.04*$B$17,-1)+D$23+D$24</f>
         <v>30570</v>
       </c>
-      <c r="E35" s="15">
+      <c r="E35" s="13">
         <f>ROUND(E$6*$B$10*0.04*$B$17,-1)+E$23+E$24</f>
         <v>152850</v>
       </c>
-      <c r="F35" s="1"/>
+      <c r="F35" s="28"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B36" s="15">
+      <c r="B36" s="13">
         <f>ROUND(B$6*$B$10*0.05*$B$17,-1)+B$23+B$24</f>
         <v>4800</v>
       </c>
-      <c r="C36" s="15">
+      <c r="C36" s="13">
         <f>ROUND(C$6*$B$10*0.05*$B$17,-1)+C$23+C$24</f>
         <v>17100</v>
       </c>
-      <c r="D36" s="15">
+      <c r="D36" s="13">
         <f>ROUND(D$6*$B$10*0.05*$B$17,-1)+D$23+D$24</f>
         <v>35270</v>
       </c>
-      <c r="E36" s="15">
+      <c r="E36" s="13">
         <f>ROUND(E$6*$B$10*0.05*$B$17,-1)+E$23+E$24</f>
         <v>176380</v>
       </c>
-      <c r="F36" s="1"/>
+      <c r="F36" s="28"/>
     </row>
     <row r="38" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="27"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="2">
